--- a/outputs/figure_source_data/source_data_fig_4_b.xlsx
+++ b/outputs/figure_source_data/source_data_fig_4_b.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% confidence intervals.</t>
+          <t>Wilson 90% confidence intervals; every expert denominator is 140 item judgments.</t>
         </is>
       </c>
     </row>
@@ -631,14 +631,14 @@
         <v>0.4928571428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.411345857883062</v>
+        <v>0.4241537529258178</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5747499449793583</v>
+        <v>0.5618313745500231</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% CI</t>
+          <t>Wilson 90% CI</t>
         </is>
       </c>
     </row>
@@ -662,14 +662,14 @@
         <v>0.4642857142857143</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.383732478121069</v>
+        <v>0.39628962888856</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.546746536191032</v>
+        <v>0.5336360084906444</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% CI</t>
+          <t>Wilson 90% CI</t>
         </is>
       </c>
     </row>
@@ -693,14 +693,14 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3495844356842501</v>
+        <v>0.3617726073060322</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.5113735929399517</v>
+        <v>0.4980786674523764</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% CI</t>
+          <t>Wilson 90% CI</t>
         </is>
       </c>
     </row>
